--- a/Colecciones.xlsx
+++ b/Colecciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nat\GitHub\collection-catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1946CDDE-7F19-459D-8341-7913D2305D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF02CE7E-A07B-404B-A734-EC47A86D41FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="16305" xr2:uid="{81597CA8-F6AF-4AD2-B5D3-D765A2B6121E}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="16305" xr2:uid="{81597CA8-F6AF-4AD2-B5D3-D765A2B6121E}"/>
   </bookViews>
   <sheets>
     <sheet name="Mis tapitas" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="131">
   <si>
     <t>id</t>
   </si>
@@ -293,18 +293,12 @@
     <t>Cerveza Especial</t>
   </si>
   <si>
-    <t>Corona sobre fondo dorado</t>
-  </si>
-  <si>
     <t>Un oso!</t>
   </si>
   <si>
     <t>Andes</t>
   </si>
   <si>
-    <t>Corona abstracta sobre fondo rojo????</t>
-  </si>
-  <si>
     <t>lugar de adquisición</t>
   </si>
   <si>
@@ -417,6 +411,27 @@
   </si>
   <si>
     <t>Un tributo a una profesora que tuve (?)</t>
+  </si>
+  <si>
+    <t>Esta parece que fue alguna edición especial. Cómico que no tengo la edición normal.</t>
+  </si>
+  <si>
+    <t>Budweiser</t>
+  </si>
+  <si>
+    <t>Imperial</t>
+  </si>
+  <si>
+    <t>Como Darth Vader.</t>
+  </si>
+  <si>
+    <t>Taa Taa Taa Taatatá Taatatá</t>
+  </si>
+  <si>
+    <t>Bear Beer</t>
+  </si>
+  <si>
+    <t>???</t>
   </si>
 </sst>
 </file>
@@ -827,7 +842,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -841,13 +856,13 @@
         <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
         <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F2" t="str">
         <f t="shared" ref="F2:F42" si="0">_xlfn.CONCAT("tapitas/",A2,".jpg")</f>
@@ -865,7 +880,7 @@
         <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F3" t="str">
         <f t="shared" si="0"/>
@@ -883,7 +898,7 @@
         <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" si="0"/>
@@ -901,7 +916,7 @@
         <v>52</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F5" t="str">
         <f t="shared" si="0"/>
@@ -919,7 +934,7 @@
         <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F6" t="str">
         <f t="shared" si="0"/>
@@ -937,7 +952,7 @@
         <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="0"/>
@@ -955,7 +970,7 @@
         <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F8" t="str">
         <f t="shared" si="0"/>
@@ -973,7 +988,7 @@
         <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" si="0"/>
@@ -985,10 +1000,13 @@
         <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>126</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="F10" t="str">
         <f t="shared" si="0"/>
@@ -1000,13 +1018,16 @@
         <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>83</v>
       </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="0"/>
@@ -1018,10 +1039,13 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>129</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F12" t="str">
         <f t="shared" si="0"/>
@@ -1035,8 +1059,11 @@
       <c r="B13" t="s">
         <v>82</v>
       </c>
+      <c r="D13" t="s">
+        <v>130</v>
+      </c>
       <c r="E13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="0"/>
@@ -1048,10 +1075,13 @@
         <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>125</v>
+      </c>
+      <c r="D14" t="s">
+        <v>52</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="F14" t="str">
         <f t="shared" si="0"/>
@@ -1072,7 +1102,7 @@
         <v>61</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F15" t="str">
         <f t="shared" si="0"/>
@@ -1090,7 +1120,7 @@
         <v>52</v>
       </c>
       <c r="E16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F16" t="str">
         <f t="shared" si="0"/>
@@ -1111,7 +1141,7 @@
         <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F17" t="str">
         <f t="shared" si="0"/>
@@ -1132,7 +1162,7 @@
         <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F18" t="str">
         <f t="shared" si="0"/>
@@ -1153,7 +1183,7 @@
         <v>52</v>
       </c>
       <c r="E19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F19" t="str">
         <f t="shared" si="0"/>
@@ -1171,7 +1201,7 @@
         <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F20" t="str">
         <f t="shared" si="0"/>
@@ -1189,7 +1219,7 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F21" t="str">
         <f t="shared" si="0"/>
@@ -1207,7 +1237,7 @@
         <v>52</v>
       </c>
       <c r="E22" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F22" t="str">
         <f t="shared" si="0"/>
@@ -1219,7 +1249,7 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C23" s="3">
         <v>1906</v>
@@ -1228,7 +1258,7 @@
         <v>61</v>
       </c>
       <c r="E23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F23" t="str">
         <f t="shared" si="0"/>
@@ -1246,7 +1276,7 @@
         <v>52</v>
       </c>
       <c r="E24" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F24" t="str">
         <f t="shared" si="0"/>
@@ -1264,7 +1294,7 @@
         <v>52</v>
       </c>
       <c r="E25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F25" t="str">
         <f t="shared" si="0"/>
@@ -1285,7 +1315,7 @@
         <v>52</v>
       </c>
       <c r="E26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F26" t="str">
         <f t="shared" si="0"/>
@@ -1303,7 +1333,7 @@
         <v>52</v>
       </c>
       <c r="E27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F27" t="str">
         <f t="shared" si="0"/>
@@ -1321,7 +1351,7 @@
         <v>52</v>
       </c>
       <c r="E28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F28" t="str">
         <f t="shared" si="0"/>
@@ -1339,7 +1369,7 @@
         <v>52</v>
       </c>
       <c r="E29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F29" t="str">
         <f t="shared" si="0"/>
@@ -1357,7 +1387,7 @@
         <v>61</v>
       </c>
       <c r="E30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F30" t="str">
         <f t="shared" si="0"/>
@@ -1396,7 +1426,7 @@
         <v>61</v>
       </c>
       <c r="E32" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F32" t="str">
         <f t="shared" si="0"/>
@@ -1417,7 +1447,7 @@
         <v>52</v>
       </c>
       <c r="E33" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F33" t="str">
         <f t="shared" si="0"/>
@@ -1438,7 +1468,7 @@
         <v>52</v>
       </c>
       <c r="E34" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F34" t="str">
         <f t="shared" si="0"/>
@@ -1459,7 +1489,7 @@
         <v>52</v>
       </c>
       <c r="E35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F35" t="str">
         <f t="shared" si="0"/>
@@ -1480,7 +1510,7 @@
         <v>52</v>
       </c>
       <c r="E36" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F36" t="str">
         <f t="shared" si="0"/>
@@ -1501,7 +1531,7 @@
         <v>52</v>
       </c>
       <c r="E37" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F37" t="str">
         <f t="shared" si="0"/>
@@ -1519,7 +1549,7 @@
         <v>52</v>
       </c>
       <c r="E38" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F38" t="str">
         <f t="shared" si="0"/>
@@ -1537,7 +1567,7 @@
         <v>52</v>
       </c>
       <c r="E39" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F39" t="str">
         <f t="shared" si="0"/>
@@ -1555,7 +1585,7 @@
         <v>52</v>
       </c>
       <c r="E40" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F40" t="str">
         <f t="shared" si="0"/>
@@ -1573,7 +1603,7 @@
         <v>52</v>
       </c>
       <c r="E41" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F41" t="str">
         <f t="shared" si="0"/>
@@ -1591,7 +1621,7 @@
         <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F42" t="str">
         <f t="shared" si="0"/>
